--- a/sim_proj_updated/priority_stats.xlsx
+++ b/sim_proj_updated/priority_stats.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="196" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="224" uniqueCount="33">
   <si>
     <t>Parameter</t>
   </si>
@@ -97,6 +97,21 @@
   </si>
   <si>
     <t>Cumulative_pct</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Coliform</t>
+  </si>
+  <si>
+    <t>E. coli</t>
+  </si>
+  <si>
+    <t>pH</t>
   </si>
 </sst>
 </file>
@@ -361,7 +376,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B8" s="0">
         <v>18</v>
@@ -419,7 +434,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B10" s="0">
         <v>18</v>
@@ -506,7 +521,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B13" s="0">
         <v>18</v>
@@ -535,7 +550,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B14" s="0">
         <v>18</v>
@@ -622,7 +637,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B17" s="0">
         <v>0</v>
